--- a/docs/workbook-split/dateien/Berichte.xlsx
+++ b/docs/workbook-split/dateien/Berichte.xlsx
@@ -671,18 +671,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G7" s="7">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$73=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$72)/('[Bilanz.xlsx]Bilanz'!$D$73))</f>
-        <v/>
-      </c>
-      <c r="H7" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G7" s="7" t="n">
+        <v>0.0711609110560909</v>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I7" s="1" t="n"/>
-      <c r="J7" s="7">
-        <f>IF(C7="Ja",G7,"")</f>
-        <v/>
+      <c r="J7" s="7" t="n">
+        <v>0.0711609110560909</v>
       </c>
       <c r="K7" s="1" t="n"/>
       <c r="L7" s="1" t="n"/>
@@ -714,18 +713,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G8" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$72)/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H8" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G8" s="8" t="n">
+        <v>0.06643344647997949</v>
+      </c>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I8" s="1" t="n"/>
-      <c r="J8" s="8">
-        <f>IF(C8="Ja",G8,"")</f>
-        <v/>
+      <c r="J8" s="8" t="n">
+        <v>0.06643344647997949</v>
       </c>
       <c r="K8" s="1" t="n"/>
       <c r="L8" s="1" t="n"/>
@@ -757,18 +755,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G9" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$73)/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H9" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G9" s="8" t="n">
+        <v>0.9335665535200204</v>
+      </c>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I9" s="1" t="n"/>
-      <c r="J9" s="8">
-        <f>IF(C9="Ja",G9,"")</f>
-        <v/>
+      <c r="J9" s="8" t="n">
+        <v>0.9335665535200204</v>
       </c>
       <c r="K9" s="1" t="n"/>
       <c r="L9" s="1" t="n"/>
@@ -800,18 +797,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G10" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$79=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$75)/('[Bilanz.xlsx]Bilanz'!$D$79))</f>
-        <v/>
-      </c>
-      <c r="H10" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G10" s="8" t="n">
+        <v>0.001657003101163529</v>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I10" s="1" t="n"/>
-      <c r="J10" s="8">
-        <f>IF(C10="Ja",G10,"")</f>
-        <v/>
+      <c r="J10" s="8" t="n">
+        <v>0.001657003101163529</v>
       </c>
       <c r="K10" s="1" t="n"/>
       <c r="L10" s="1" t="n"/>
@@ -843,18 +839,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G11" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$79=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$75+'[Bilanz.xlsx]Bilanz'!$D$74)/('[Bilanz.xlsx]Bilanz'!$D$79))</f>
-        <v/>
-      </c>
-      <c r="H11" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G11" s="8" t="n">
+        <v>0.4584465915368146</v>
+      </c>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I11" s="1" t="n"/>
-      <c r="J11" s="8">
-        <f>IF(C11="Ja",G11,"")</f>
-        <v/>
+      <c r="J11" s="8" t="n">
+        <v>0.4584465915368146</v>
       </c>
       <c r="K11" s="1" t="n"/>
       <c r="L11" s="1" t="n"/>
@@ -886,18 +881,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G12" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$79=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$73)/('[Bilanz.xlsx]Bilanz'!$D$79))</f>
-        <v/>
-      </c>
-      <c r="H12" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G12" s="8" t="n">
+        <v>1.708898927958215</v>
+      </c>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I12" s="1" t="n"/>
-      <c r="J12" s="8">
-        <f>IF(C12="Ja",G12,"")</f>
-        <v/>
+      <c r="J12" s="8" t="n">
+        <v>1.708898927958215</v>
       </c>
       <c r="K12" s="1" t="n"/>
       <c r="L12" s="1" t="n"/>
@@ -929,18 +923,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G13" s="7">
-        <f>'[Bilanz.xlsx]Bilanz'!$D$73-'[Bilanz.xlsx]Bilanz'!$D$79</f>
-        <v/>
-      </c>
-      <c r="H13" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G13" s="7" t="n">
+        <v>2615305.929999997</v>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I13" s="1" t="n"/>
-      <c r="J13" s="7">
-        <f>IF(C13="Ja",G13,"")</f>
-        <v/>
+      <c r="J13" s="7" t="n">
+        <v>2615305.929999997</v>
       </c>
       <c r="K13" s="1" t="n"/>
       <c r="L13" s="1" t="n"/>
@@ -972,18 +965,17 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G14" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$77)/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H14" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G14" s="8" t="n">
+        <v>0.4537028853804472</v>
+      </c>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I14" s="1" t="n"/>
-      <c r="J14" s="8">
-        <f>IF(C14="Ja",G14,"")</f>
-        <v/>
+      <c r="J14" s="8" t="n">
+        <v>0.4537028853804472</v>
       </c>
       <c r="K14" s="1" t="n"/>
       <c r="L14" s="1" t="n"/>
@@ -1015,19 +1007,16 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G15" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$78)/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H15" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G15" s="8" t="n">
+        <v>0.5462971146195531</v>
+      </c>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I15" s="1" t="n"/>
-      <c r="J15" s="8">
-        <f>IF(C15="Ja",G15,"")</f>
-        <v/>
-      </c>
+      <c r="J15" s="8" t="n"/>
       <c r="K15" s="1" t="n"/>
       <c r="L15" s="1" t="n"/>
       <c r="M15" s="1" t="n"/>
@@ -1058,19 +1047,16 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G16" s="7">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$78=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$77)/('[Bilanz.xlsx]Bilanz'!$D$78))</f>
-        <v/>
-      </c>
-      <c r="H16" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G16" s="7" t="n">
+        <v>0.8305057325744992</v>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I16" s="1" t="n"/>
-      <c r="J16" s="7">
-        <f>IF(C16="Ja",G16,"")</f>
-        <v/>
-      </c>
+      <c r="J16" s="7" t="n"/>
       <c r="K16" s="1" t="n"/>
       <c r="L16" s="1" t="n"/>
       <c r="M16" s="1" t="n"/>
@@ -1101,19 +1087,16 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G17" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$77=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$78)/('[Bilanz.xlsx]Bilanz'!$D$77))</f>
-        <v/>
-      </c>
-      <c r="H17" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G17" s="8" t="n">
+        <v>1.204085608054845</v>
+      </c>
+      <c r="H17" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I17" s="1" t="n"/>
-      <c r="J17" s="8">
-        <f>IF(C17="Ja",G17,"")</f>
-        <v/>
-      </c>
+      <c r="J17" s="8" t="n"/>
       <c r="K17" s="1" t="n"/>
       <c r="L17" s="1" t="n"/>
       <c r="M17" s="1" t="n"/>
@@ -1144,19 +1127,16 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G18" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$72=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$77)/('[Bilanz.xlsx]Bilanz'!$D$72))</f>
-        <v/>
-      </c>
-      <c r="H18" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G18" s="8" t="n">
+        <v>6.829434711281702</v>
+      </c>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I18" s="1" t="n"/>
-      <c r="J18" s="8">
-        <f>IF(C18="Ja",G18,"")</f>
-        <v/>
-      </c>
+      <c r="J18" s="8" t="n"/>
       <c r="K18" s="1" t="n"/>
       <c r="L18" s="1" t="n"/>
       <c r="M18" s="1" t="n"/>
@@ -1187,23 +1167,20 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G19" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$72=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$77+'[Bilanz.xlsx]Bilanz'!$D$80)/('[Bilanz.xlsx]Bilanz'!$D$72))</f>
-        <v/>
-      </c>
-      <c r="H19" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G19" s="8" t="n">
+        <v>6.829434711281702</v>
+      </c>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I19" s="1" t="inlineStr">
         <is>
           <t>Fristigkeit nach Originalvereinfachung.</t>
         </is>
       </c>
-      <c r="J19" s="8">
-        <f>IF(C19="Ja",G19,"")</f>
-        <v/>
-      </c>
+      <c r="J19" s="8" t="n"/>
       <c r="K19" s="1" t="n"/>
       <c r="L19" s="1" t="n"/>
       <c r="M19" s="1" t="n"/>
@@ -1234,19 +1211,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G20" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$77=0,"n.a.",(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$77))</f>
-        <v/>
-      </c>
-      <c r="H20" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G20" s="8" t="n">
+        <v>-0.6972682427644817</v>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I20" s="1" t="n"/>
-      <c r="J20" s="8">
-        <f>IF(C20="Ja",G20,"")</f>
-        <v/>
-      </c>
+      <c r="J20" s="8" t="n"/>
       <c r="K20" s="1" t="n"/>
       <c r="L20" s="1" t="n"/>
       <c r="M20" s="1" t="n"/>
@@ -1277,19 +1251,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G21" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12)-($F$71/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H21" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G21" s="8" t="n">
+        <v>-0.3022315439272078</v>
+      </c>
+      <c r="H21" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I21" s="1" t="n"/>
-      <c r="J21" s="8">
-        <f>IF(C21="Ja",G21,"")</f>
-        <v/>
-      </c>
+      <c r="J21" s="8" t="n"/>
       <c r="K21" s="1" t="n"/>
       <c r="L21" s="1" t="n"/>
       <c r="M21" s="1" t="n"/>
@@ -1320,19 +1291,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G22" s="8">
-        <f>IF(D67=0,"n.a.",(D73)/(D67))</f>
-        <v/>
-      </c>
-      <c r="H22" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E67=0,"n.a.",(E73)/(E67)))</f>
-        <v/>
+      <c r="G22" s="8" t="n">
+        <v>-1.289455686343818</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>-0.1852722799395613</v>
       </c>
       <c r="I22" s="1" t="n"/>
-      <c r="J22" s="8">
-        <f>IF(C22="Ja",G22,"")</f>
-        <v/>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="1" t="n"/>
       <c r="L22" s="1" t="n"/>
       <c r="M22" s="1" t="n"/>
@@ -1363,19 +1329,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G23" s="7">
-        <f>IF(D78=0,"n.a.",(D68+D74)/(D78))</f>
-        <v/>
-      </c>
-      <c r="H23" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E78=0,"n.a.",(E68+E74)/(E78)))</f>
-        <v/>
+      <c r="G23" s="7" t="n">
+        <v>0.5129675469045394</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0.9283949118352286</v>
       </c>
       <c r="I23" s="1" t="n"/>
-      <c r="J23" s="7">
-        <f>IF(C23="Ja",G23,"")</f>
-        <v/>
-      </c>
+      <c r="J23" s="7" t="n"/>
       <c r="K23" s="1" t="n"/>
       <c r="L23" s="1" t="n"/>
       <c r="M23" s="1" t="n"/>
@@ -1406,19 +1367,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G24" s="7">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$77=0,"n.a.",(($F$67/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$77))</f>
-        <v/>
-      </c>
-      <c r="H24" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G24" s="7" t="n">
+        <v>5.304698205318223</v>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I24" s="1" t="n"/>
-      <c r="J24" s="7">
-        <f>IF(C24="Ja",G24,"")</f>
-        <v/>
-      </c>
+      <c r="J24" s="7" t="n"/>
       <c r="K24" s="1" t="n"/>
       <c r="L24" s="1" t="n"/>
       <c r="M24" s="1" t="n"/>
@@ -1449,19 +1407,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G25" s="7">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",(($F$67/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H25" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G25" s="7" t="n">
+        <v>2.406756881825358</v>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I25" s="1" t="n"/>
-      <c r="J25" s="7">
-        <f>IF(C25="Ja",G25,"")</f>
-        <v/>
-      </c>
+      <c r="J25" s="7" t="n"/>
       <c r="K25" s="1" t="n"/>
       <c r="L25" s="1" t="n"/>
       <c r="M25" s="1" t="n"/>
@@ -1492,19 +1447,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G26" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H26" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G26" s="8" t="n">
+        <v>-0.3163526136263995</v>
+      </c>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I26" s="1" t="n"/>
-      <c r="J26" s="8">
-        <f>IF(C26="Ja",G26,"")</f>
-        <v/>
-      </c>
+      <c r="J26" s="8" t="n"/>
       <c r="K26" s="1" t="n"/>
       <c r="L26" s="1" t="n"/>
       <c r="M26" s="1" t="n"/>
@@ -1535,19 +1487,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G27" s="7">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$74=0,"n.a.",(($F$67/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$74))</f>
-        <v/>
-      </c>
-      <c r="H27" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G27" s="7" t="n">
+        <v>9.644664372018774</v>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I27" s="1" t="n"/>
-      <c r="J27" s="7">
-        <f>IF(C27="Ja",G27,"")</f>
-        <v/>
-      </c>
+      <c r="J27" s="7" t="n"/>
       <c r="K27" s="1" t="n"/>
       <c r="L27" s="1" t="n"/>
       <c r="M27" s="1" t="n"/>
@@ -1578,19 +1527,16 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G28" s="8">
-        <f>IF(SUMIFS('[D Liquidität.xlsx]D Liquidität'!$I$282:$I$626,'[D Liquidität.xlsx]D Liquidität'!$B$282:$B$626,"FORDERUNG")=0,"n.a.",(SUMIFS('[D Liquidität.xlsx]D Liquidität'!$I$282:$I$626,'[D Liquidität.xlsx]D Liquidität'!$B$282:$B$626,"FORDERUNG",'[D Liquidität.xlsx]D Liquidität'!$H$282:$H$626,"&lt;"&amp;TEXT('[Steuerung.xlsx]Steuerung'!$F$12,"yyyy-mm-dd")))/(SUMIFS('[D Liquidität.xlsx]D Liquidität'!$I$282:$I$626,'[D Liquidität.xlsx]D Liquidität'!$B$282:$B$626,"FORDERUNG")))</f>
-        <v/>
-      </c>
-      <c r="H28" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G28" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I28" s="1" t="n"/>
-      <c r="J28" s="8">
-        <f>IF(C28="Ja",G28,"")</f>
-        <v/>
-      </c>
+      <c r="J28" s="8" t="n"/>
       <c r="K28" s="1" t="n"/>
       <c r="L28" s="1" t="n"/>
       <c r="M28" s="1" t="n"/>
@@ -1621,19 +1567,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G29" s="7">
-        <f>IF(($F$67/'[Steuerung.xlsx]Steuerung'!$F$7*12)=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$74*365)/(($F$67/'[Steuerung.xlsx]Steuerung'!$F$7*12)))</f>
-        <v/>
-      </c>
-      <c r="H29" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G29" s="7" t="n">
+        <v>37.84475912494609</v>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I29" s="1" t="n"/>
-      <c r="J29" s="7">
-        <f>IF(C29="Ja",G29,"")</f>
-        <v/>
-      </c>
+      <c r="J29" s="7" t="n"/>
       <c r="K29" s="1" t="n"/>
       <c r="L29" s="1" t="n"/>
       <c r="M29" s="1" t="n"/>
@@ -1664,19 +1607,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G30" s="7">
-        <f>IF(($F$75/'[Steuerung.xlsx]Steuerung'!$F$7*12)=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$81*365)/(($F$75/'[Steuerung.xlsx]Steuerung'!$F$7*12)))</f>
-        <v/>
-      </c>
-      <c r="H30" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G30" s="7" t="n">
+        <v>28.61283756332094</v>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I30" s="1" t="n"/>
-      <c r="J30" s="7">
-        <f>IF(C30="Ja",G30,"")</f>
-        <v/>
-      </c>
+      <c r="J30" s="7" t="n"/>
       <c r="K30" s="1" t="n"/>
       <c r="L30" s="1" t="n"/>
       <c r="M30" s="1" t="n"/>
@@ -1707,19 +1647,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G31" s="7">
-        <f>IF(D68=0,"n.a.",(ABS(D86)*30)/(D68))</f>
-        <v/>
-      </c>
-      <c r="H31" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E68=0,"n.a.",(ABS(E86)*30)/(E68)))</f>
-        <v/>
+      <c r="G31" s="7" t="n">
+        <v>47.57461900289424</v>
+      </c>
+      <c r="H31" s="7" t="n">
+        <v>18.63480414025307</v>
       </c>
       <c r="I31" s="1" t="n"/>
-      <c r="J31" s="7">
-        <f>IF(C31="Ja",G31,"")</f>
-        <v/>
-      </c>
+      <c r="J31" s="7" t="n"/>
       <c r="K31" s="1" t="n"/>
       <c r="L31" s="1" t="n"/>
       <c r="M31" s="1" t="n"/>
@@ -1750,19 +1685,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G32" s="7">
-        <f>D73-D70</f>
-        <v/>
-      </c>
-      <c r="H32" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",E73-E70)</f>
-        <v/>
+      <c r="G32" s="7" t="n">
+        <v>-1132559.77</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>-149175.64</v>
       </c>
       <c r="I32" s="1" t="n"/>
-      <c r="J32" s="7">
-        <f>IF(C32="Ja",G32,"")</f>
-        <v/>
-      </c>
+      <c r="J32" s="7" t="n"/>
       <c r="K32" s="1" t="n"/>
       <c r="L32" s="1" t="n"/>
       <c r="M32" s="1" t="n"/>
@@ -1793,19 +1723,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G33" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$72=0,"n.a.",(-D70)/('[Bilanz.xlsx]Bilanz'!$D$72))</f>
-        <v/>
-      </c>
-      <c r="H33" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF('[Bilanz.xlsx]Bilanz'!$D$72=0,"n.a.",(-E70)/('[Bilanz.xlsx]Bilanz'!$D$72)))</f>
-        <v/>
+      <c r="G33" s="8" t="n">
+        <v>0.0202880718976101</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0.02030556930086172</v>
       </c>
       <c r="I33" s="1" t="n"/>
-      <c r="J33" s="8">
-        <f>IF(C33="Ja",G33,"")</f>
-        <v/>
-      </c>
+      <c r="J33" s="8" t="n"/>
       <c r="K33" s="1" t="n"/>
       <c r="L33" s="1" t="n"/>
       <c r="M33" s="1" t="n"/>
@@ -1836,19 +1761,16 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G34" s="7">
-        <f>IF(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12)-($F$70/'[Steuerung.xlsx]Steuerung'!$F$7*12)=0,"n.a.",('[Bilanz.xlsx]Bilanz'!$D$78)/(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12)-($F$70/'[Steuerung.xlsx]Steuerung'!$F$7*12)))</f>
-        <v/>
-      </c>
-      <c r="H34" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G34" s="7" t="n">
+        <v>-1.823335725930179</v>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I34" s="1" t="n"/>
-      <c r="J34" s="7">
-        <f>IF(C34="Ja",G34,"")</f>
-        <v/>
-      </c>
+      <c r="J34" s="7" t="n"/>
       <c r="K34" s="1" t="n"/>
       <c r="L34" s="1" t="n"/>
       <c r="M34" s="1" t="n"/>
@@ -1879,23 +1801,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G35" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H35" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G35" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I35" s="1" t="inlineStr">
         <is>
           <t>Beschäftigungsarten fehlen.</t>
         </is>
       </c>
-      <c r="J35" s="7">
-        <f>IF(C35="Ja",G35,"")</f>
-        <v/>
-      </c>
+      <c r="J35" s="7" t="n"/>
       <c r="K35" s="1" t="n"/>
       <c r="L35" s="1" t="n"/>
       <c r="M35" s="1" t="n"/>
@@ -1926,19 +1847,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G36" s="8">
-        <f>IF(ISNUMBER(D80),IF(D80=0,"n.a.",(D79)/(D80)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H36" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E80),IF(E80=0,"n.a.",(E79)/(E80)),"n.a."))</f>
-        <v/>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I36" s="1" t="n"/>
-      <c r="J36" s="8">
-        <f>IF(C36="Ja",G36,"")</f>
-        <v/>
-      </c>
+      <c r="J36" s="8" t="n"/>
       <c r="K36" s="1" t="n"/>
       <c r="L36" s="1" t="n"/>
       <c r="M36" s="1" t="n"/>
@@ -1969,19 +1889,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G37" s="8">
-        <f>IF(D78=0,"n.a.",(D76)/(D78))</f>
-        <v/>
-      </c>
-      <c r="H37" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E78=0,"n.a.",(E76)/(E78)))</f>
-        <v/>
+      <c r="G37" s="8" t="n">
+        <v>0.1511737738470084</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0.1959392704105254</v>
       </c>
       <c r="I37" s="1" t="n"/>
-      <c r="J37" s="8">
-        <f>IF(C37="Ja",G37,"")</f>
-        <v/>
-      </c>
+      <c r="J37" s="8" t="n"/>
       <c r="K37" s="1" t="n"/>
       <c r="L37" s="1" t="n"/>
       <c r="M37" s="1" t="n"/>
@@ -2012,19 +1927,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G38" s="8">
-        <f>IF(D68=0,"n.a.",(D76)/(D68))</f>
-        <v/>
-      </c>
-      <c r="H38" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E68=0,"n.a.",(E76)/(E68)))</f>
-        <v/>
+      <c r="G38" s="8" t="n">
+        <v>0.4029630418240266</v>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>0.2126575668751622</v>
       </c>
       <c r="I38" s="1" t="n"/>
-      <c r="J38" s="8">
-        <f>IF(C38="Ja",G38,"")</f>
-        <v/>
-      </c>
+      <c r="J38" s="8" t="n"/>
       <c r="K38" s="1" t="n"/>
       <c r="L38" s="1" t="n"/>
       <c r="M38" s="1" t="n"/>
@@ -2055,19 +1965,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G39" s="8">
-        <f>IF(ISNUMBER(D80),IF(D80=0,"n.a.",(D81)/(D80)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H39" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E80),IF(E80=0,"n.a.",(E81)/(E80)),"n.a."))</f>
-        <v/>
+      <c r="G39" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I39" s="1" t="n"/>
-      <c r="J39" s="8">
-        <f>IF(C39="Ja",G39,"")</f>
-        <v/>
-      </c>
+      <c r="J39" s="8" t="n"/>
       <c r="K39" s="1" t="n"/>
       <c r="L39" s="1" t="n"/>
       <c r="M39" s="1" t="n"/>
@@ -2098,23 +2007,22 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G40" s="7">
-        <f>IF(ISNUMBER(D80),TEXT(D82/D80,"0%")&amp;" / "&amp;TEXT(D81/D80,"0%")&amp;" / "&amp;TEXT(D83/D80,"0%"),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H40" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E80),TEXT(E82/E80,"0%")&amp;" / "&amp;TEXT(E81/E80,"0%")&amp;" / "&amp;TEXT(E83/E80,"0%"),"n.a."))</f>
-        <v/>
+      <c r="G40" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I40" s="1" t="inlineStr">
         <is>
           <t>Urlaub / Krankheit / Feiertag.</t>
         </is>
       </c>
-      <c r="J40" s="7">
-        <f>IF(C40="Ja",G40,"")</f>
-        <v/>
-      </c>
+      <c r="J40" s="7" t="n"/>
       <c r="K40" s="1" t="n"/>
       <c r="L40" s="1" t="n"/>
       <c r="M40" s="1" t="n"/>
@@ -2145,19 +2053,14 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G41" s="8">
-        <f>IF(D67=0,"n.a.",(D76)/(D67))</f>
-        <v/>
-      </c>
-      <c r="H41" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(E67=0,"n.a.",(E76)/(E67)))</f>
-        <v/>
+      <c r="G41" s="8" t="n">
+        <v>0.4029630418240266</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0.4671788921841687</v>
       </c>
       <c r="I41" s="1" t="n"/>
-      <c r="J41" s="8">
-        <f>IF(C41="Ja",G41,"")</f>
-        <v/>
-      </c>
+      <c r="J41" s="8" t="n"/>
       <c r="K41" s="1" t="n"/>
       <c r="L41" s="1" t="n"/>
       <c r="M41" s="1" t="n"/>
@@ -2188,19 +2091,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G42" s="7">
-        <f>IF(ISNUMBER(D85),IF(D85=0,"n.a.",(D67)/(D85)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H42" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E85),IF(E85=0,"n.a.",(E67)/(E85)),"n.a."))</f>
-        <v/>
+      <c r="G42" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I42" s="1" t="n"/>
-      <c r="J42" s="7">
-        <f>IF(C42="Ja",G42,"")</f>
-        <v/>
-      </c>
+      <c r="J42" s="7" t="n"/>
       <c r="K42" s="1" t="n"/>
       <c r="L42" s="1" t="n"/>
       <c r="M42" s="1" t="n"/>
@@ -2231,23 +2133,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G43" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H43" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G43" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
         <is>
           <t>Ein- und Austritte fehlen.</t>
         </is>
       </c>
-      <c r="J43" s="7">
-        <f>IF(C43="Ja",G43,"")</f>
-        <v/>
-      </c>
+      <c r="J43" s="7" t="n"/>
       <c r="K43" s="1" t="n"/>
       <c r="L43" s="1" t="n"/>
       <c r="M43" s="1" t="n"/>
@@ -2278,23 +2179,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G44" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H44" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G44" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I44" s="1" t="inlineStr">
         <is>
           <t>Keine separate Kostenzuordnung.</t>
         </is>
       </c>
-      <c r="J44" s="7">
-        <f>IF(C44="Ja",G44,"")</f>
-        <v/>
-      </c>
+      <c r="J44" s="7" t="n"/>
       <c r="K44" s="1" t="n"/>
       <c r="L44" s="1" t="n"/>
       <c r="M44" s="1" t="n"/>
@@ -2325,19 +2225,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G45" s="8">
-        <f>IF(ISNUMBER(D80),IF(D80=0,"n.a.",(SUM(D81:D84))/(D80)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H45" s="8">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E80),IF(E80=0,"n.a.",(SUM(E81:E84))/(E80)),"n.a."))</f>
-        <v/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I45" s="1" t="n"/>
-      <c r="J45" s="8">
-        <f>IF(C45="Ja",G45,"")</f>
-        <v/>
-      </c>
+      <c r="J45" s="8" t="n"/>
       <c r="K45" s="1" t="n"/>
       <c r="L45" s="1" t="n"/>
       <c r="M45" s="1" t="n"/>
@@ -2368,19 +2267,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G46" s="7">
-        <f>IF(ISNUMBER(D85),IF(D85=0,"n.a.",(D76)/(D85)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H46" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E85),IF(E85=0,"n.a.",(E76)/(E85)),"n.a."))</f>
-        <v/>
+      <c r="G46" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I46" s="1" t="n"/>
-      <c r="J46" s="7">
-        <f>IF(C46="Ja",G46,"")</f>
-        <v/>
-      </c>
+      <c r="J46" s="7" t="n"/>
       <c r="K46" s="1" t="n"/>
       <c r="L46" s="1" t="n"/>
       <c r="M46" s="1" t="n"/>
@@ -2411,19 +2309,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G47" s="7">
-        <f>IF(ISNUMBER(D85),IF(D85=0,"n.a.",(D68)/(D85)),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="H47" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(ISNUMBER(E85),IF(E85=0,"n.a.",(E68)/(E85)),"n.a."))</f>
-        <v/>
+      <c r="G47" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I47" s="1" t="n"/>
-      <c r="J47" s="7">
-        <f>IF(C47="Ja",G47,"")</f>
-        <v/>
-      </c>
+      <c r="J47" s="7" t="n"/>
       <c r="K47" s="1" t="n"/>
       <c r="L47" s="1" t="n"/>
       <c r="M47" s="1" t="n"/>
@@ -2454,23 +2351,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G48" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H48" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G48" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I48" s="1" t="inlineStr">
         <is>
           <t>Geburtsdaten fehlen.</t>
         </is>
       </c>
-      <c r="J48" s="7">
-        <f>IF(C48="Ja",G48,"")</f>
-        <v/>
-      </c>
+      <c r="J48" s="7" t="n"/>
       <c r="K48" s="1" t="n"/>
       <c r="L48" s="1" t="n"/>
       <c r="M48" s="1" t="n"/>
@@ -2501,23 +2397,20 @@
           <t>YTD annualisiert</t>
         </is>
       </c>
-      <c r="G49" s="8">
-        <f>IF('[Bilanz.xlsx]Bilanz'!$D$83=0,"n.a.",(($F$73/'[Steuerung.xlsx]Steuerung'!$F$7*12))/('[Bilanz.xlsx]Bilanz'!$D$83))</f>
-        <v/>
-      </c>
-      <c r="H49" s="8">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G49" s="8" t="n">
+        <v>-0.3163526136263995</v>
+      </c>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I49" s="1" t="inlineStr">
         <is>
           <t>Umsatzrendite × Kapitalumschlag.</t>
         </is>
       </c>
-      <c r="J49" s="8">
-        <f>IF(C49="Ja",G49,"")</f>
-        <v/>
-      </c>
+      <c r="J49" s="8" t="n"/>
       <c r="K49" s="1" t="n"/>
       <c r="L49" s="1" t="n"/>
       <c r="M49" s="1" t="n"/>
@@ -2548,19 +2441,18 @@
           <t>Übersicht</t>
         </is>
       </c>
-      <c r="G50" s="7">
-        <f>"Cockpit / Vertrieb / Stunden"</f>
-        <v/>
-      </c>
-      <c r="H50" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G50" s="7" t="inlineStr">
+        <is>
+          <t>Cockpit / Vertrieb / Stunden</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I50" s="1" t="n"/>
-      <c r="J50" s="7">
-        <f>IF(C50="Ja",G50,"")</f>
-        <v/>
-      </c>
+      <c r="J50" s="7" t="n"/>
       <c r="K50" s="1" t="n"/>
       <c r="L50" s="1" t="n"/>
       <c r="M50" s="1" t="n"/>
@@ -2591,19 +2483,18 @@
           <t>Stichtag</t>
         </is>
       </c>
-      <c r="G51" s="7">
-        <f>"Blatt Bilanz"</f>
-        <v/>
-      </c>
-      <c r="H51" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G51" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Bilanz</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I51" s="1" t="n"/>
-      <c r="J51" s="7">
-        <f>IF(C51="Ja",G51,"")</f>
-        <v/>
-      </c>
+      <c r="J51" s="7" t="n"/>
       <c r="K51" s="1" t="n"/>
       <c r="L51" s="1" t="n"/>
       <c r="M51" s="1" t="n"/>
@@ -2634,19 +2525,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G52" s="7">
-        <f>"Blatt GuV"</f>
-        <v/>
-      </c>
-      <c r="H52" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.","Blatt GuV")</f>
-        <v/>
+      <c r="G52" s="7" t="inlineStr">
+        <is>
+          <t>Blatt GuV</t>
+        </is>
+      </c>
+      <c r="H52" s="7" t="inlineStr">
+        <is>
+          <t>Blatt GuV</t>
+        </is>
       </c>
       <c r="I52" s="1" t="n"/>
-      <c r="J52" s="7">
-        <f>IF(C52="Ja",G52,"")</f>
-        <v/>
-      </c>
+      <c r="J52" s="7" t="n"/>
       <c r="K52" s="1" t="n"/>
       <c r="L52" s="1" t="n"/>
       <c r="M52" s="1" t="n"/>
@@ -2677,19 +2567,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G53" s="7">
-        <f>"Blatt Fremdleistungen"</f>
-        <v/>
-      </c>
-      <c r="H53" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.","Blatt Fremdleistungen")</f>
-        <v/>
+      <c r="G53" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Fremdleistungen</t>
+        </is>
+      </c>
+      <c r="H53" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Fremdleistungen</t>
+        </is>
       </c>
       <c r="I53" s="1" t="n"/>
-      <c r="J53" s="7">
-        <f>IF(C53="Ja",G53,"")</f>
-        <v/>
-      </c>
+      <c r="J53" s="7" t="n"/>
       <c r="K53" s="1" t="n"/>
       <c r="L53" s="1" t="n"/>
       <c r="M53" s="1" t="n"/>
@@ -2720,19 +2609,18 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G54" s="7">
-        <f>"Blatt Forecast"</f>
-        <v/>
-      </c>
-      <c r="H54" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.","Blatt Forecast")</f>
-        <v/>
+      <c r="G54" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Forecast</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Forecast</t>
+        </is>
       </c>
       <c r="I54" s="1" t="n"/>
-      <c r="J54" s="7">
-        <f>IF(C54="Ja",G54,"")</f>
-        <v/>
-      </c>
+      <c r="J54" s="7" t="n"/>
       <c r="K54" s="1" t="n"/>
       <c r="L54" s="1" t="n"/>
       <c r="M54" s="1" t="n"/>
@@ -2763,19 +2651,18 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="G55" s="7">
-        <f>"Blatt Regionen"</f>
-        <v/>
-      </c>
-      <c r="H55" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G55" s="7" t="inlineStr">
+        <is>
+          <t>Blatt Regionen</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I55" s="1" t="n"/>
-      <c r="J55" s="7">
-        <f>IF(C55="Ja",G55,"")</f>
-        <v/>
-      </c>
+      <c r="J55" s="7" t="n"/>
       <c r="K55" s="1" t="n"/>
       <c r="L55" s="1" t="n"/>
       <c r="M55" s="1" t="n"/>
@@ -2806,19 +2693,16 @@
           <t>Monat</t>
         </is>
       </c>
-      <c r="G56" s="7">
-        <f>IF(OR(D68=0,1-D75/D68&lt;=0),"n.a.",(D76+D77-D70)/(1-D75/D68))</f>
-        <v/>
-      </c>
-      <c r="H56" s="7">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(E68=0,1-E75/E68&lt;=0),"n.a.",(E76+E77-E70)/(1-E75/E68)))</f>
-        <v/>
+      <c r="G56" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>2559991.297542483</v>
       </c>
       <c r="I56" s="1" t="n"/>
-      <c r="J56" s="7">
-        <f>IF(C56="Ja",G56,"")</f>
-        <v/>
-      </c>
+      <c r="J56" s="7" t="n"/>
       <c r="K56" s="1" t="n"/>
       <c r="L56" s="1" t="n"/>
       <c r="M56" s="1" t="n"/>
@@ -2849,23 +2733,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G57" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H57" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G57" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I57" s="1" t="inlineStr">
         <is>
           <t>Marktvolumen fehlt.</t>
         </is>
       </c>
-      <c r="J57" s="7">
-        <f>IF(C57="Ja",G57,"")</f>
-        <v/>
-      </c>
+      <c r="J57" s="7" t="n"/>
       <c r="K57" s="1" t="n"/>
       <c r="L57" s="1" t="n"/>
       <c r="M57" s="1" t="n"/>
@@ -2896,23 +2779,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G58" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H58" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G58" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I58" s="1" t="inlineStr">
         <is>
           <t>Wettbewerberdaten fehlen.</t>
         </is>
       </c>
-      <c r="J58" s="7">
-        <f>IF(C58="Ja",G58,"")</f>
-        <v/>
-      </c>
+      <c r="J58" s="7" t="n"/>
       <c r="K58" s="1" t="n"/>
       <c r="L58" s="1" t="n"/>
       <c r="M58" s="1" t="n"/>
@@ -2943,23 +2825,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G59" s="7">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H59" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G59" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I59" s="1" t="inlineStr">
         <is>
           <t>Marktvolumen fehlt.</t>
         </is>
       </c>
-      <c r="J59" s="7">
-        <f>IF(C59="Ja",G59,"")</f>
-        <v/>
-      </c>
+      <c r="J59" s="7" t="n"/>
       <c r="K59" s="1" t="n"/>
       <c r="L59" s="1" t="n"/>
       <c r="M59" s="1" t="n"/>
@@ -2990,19 +2871,16 @@
           <t>YTD</t>
         </is>
       </c>
-      <c r="G60" s="7">
-        <f>IF($F$67/'[Steuerung.xlsx]Steuerung'!$F$7=0,"n.a.",(SUM('[D Finanzen.xlsx]D Finanzen'!$H$444:$H$617))/($F$67/'[Steuerung.xlsx]Steuerung'!$F$7))</f>
-        <v/>
-      </c>
-      <c r="H60" s="7">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G60" s="7" t="n">
+        <v>5.0101418597025</v>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I60" s="1" t="n"/>
-      <c r="J60" s="7">
-        <f>IF(C60="Ja",G60,"")</f>
-        <v/>
-      </c>
+      <c r="J60" s="7" t="n"/>
       <c r="K60" s="1" t="n"/>
       <c r="L60" s="1" t="n"/>
       <c r="M60" s="1" t="n"/>
@@ -3031,23 +2909,22 @@
           <t>Nicht verfügbar</t>
         </is>
       </c>
-      <c r="G61" s="10">
-        <f>"n.a."</f>
-        <v/>
-      </c>
-      <c r="H61" s="10">
-        <f>"n.a."</f>
-        <v/>
+      <c r="G61" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="H61" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>Neukundenzählung fehlt.</t>
         </is>
       </c>
-      <c r="J61" s="10">
-        <f>IF(C61="Ja",G61,"")</f>
-        <v/>
-      </c>
+      <c r="J61" s="10" t="n"/>
     </row>
     <row r="62"/>
     <row r="63"/>
@@ -3081,17 +2958,14 @@
           <t>Umsatz</t>
         </is>
       </c>
-      <c r="D67" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$7:$Q$7,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E67" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$7:$Q$7,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F67" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D7</f>
-        <v/>
+      <c r="D67" s="10" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="E67" s="10" t="n">
+        <v>854339.84</v>
+      </c>
+      <c r="F67" s="10" t="n">
+        <v>12189973.4</v>
       </c>
     </row>
     <row r="68">
@@ -3100,17 +2974,14 @@
           <t>Gesamtleistung</t>
         </is>
       </c>
-      <c r="D68" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$9:$Q$9,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E68" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$9:$Q$9,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F68" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D9</f>
-        <v/>
+      <c r="D68" s="10" t="n">
+        <v>885382.71</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>1876864.98</v>
+      </c>
+      <c r="F68" s="10" t="n">
+        <v>17098817.86</v>
       </c>
     </row>
     <row r="69">
@@ -3119,17 +2990,14 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="D69" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$20:$Q$20,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E69" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$20:$Q$20,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F69" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D20</f>
-        <v/>
+      <c r="D69" s="10" t="n">
+        <v>-1453149.19</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>-138242.37</v>
+      </c>
+      <c r="F69" s="10" t="n">
+        <v>-1711536.9</v>
       </c>
     </row>
     <row r="70">
@@ -3138,17 +3006,14 @@
           <t>Abschreibungen</t>
         </is>
       </c>
-      <c r="D70" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$15:$Q$15,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E70" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$15:$Q$15,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F70" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D15</f>
-        <v/>
+      <c r="D70" s="10" t="n">
+        <v>-9102</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>-9109.85</v>
+      </c>
+      <c r="F70" s="10" t="n">
+        <v>-84778.77</v>
       </c>
     </row>
     <row r="71">
@@ -3157,17 +3022,14 @@
           <t>Finanzergebnis</t>
         </is>
       </c>
-      <c r="D71" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$17:$Q$17,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E71" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$17:$Q$17,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F71" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D17</f>
-        <v/>
+      <c r="D71" s="10" t="n">
+        <v>8366</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>-12425.47</v>
+      </c>
+      <c r="F71" s="10" t="n">
+        <v>-71521.75</v>
       </c>
     </row>
     <row r="72">
@@ -3176,17 +3038,14 @@
           <t>Neutrales Ergebnis</t>
         </is>
       </c>
-      <c r="D72" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$24:$Q$24,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E72" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$24:$Q$24,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F72" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D24</f>
-        <v/>
+      <c r="D72" s="10" t="n">
+        <v>312223.42</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>1492.2</v>
+      </c>
+      <c r="F72" s="10" t="n">
+        <v>265544.3199999999</v>
       </c>
     </row>
     <row r="73">
@@ -3195,17 +3054,14 @@
           <t>Ergebnis</t>
         </is>
       </c>
-      <c r="D73" s="10">
-        <f>SUM(D69:D72)</f>
-        <v/>
-      </c>
-      <c r="E73" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",SUM(E69:E72))</f>
-        <v/>
-      </c>
-      <c r="F73" s="10">
-        <f>SUM(F69:F72)</f>
-        <v/>
+      <c r="D73" s="10" t="n">
+        <v>-1141661.77</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>-158285.49</v>
+      </c>
+      <c r="F73" s="10" t="n">
+        <v>-1602293.1</v>
       </c>
     </row>
     <row r="74">
@@ -3214,17 +3070,14 @@
           <t>Sonstige Erträge</t>
         </is>
       </c>
-      <c r="D74" s="10">
-        <f>1*INDEX('[GuV.xlsx]GuV'!$F$10:$Q$10,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E74" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",1*INDEX('[GuV.xlsx]GuV'!$F$10:$Q$10,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F74" s="10">
-        <f>1*'[GuV.xlsx]GuV'!D10</f>
-        <v/>
+      <c r="D74" s="10" t="n">
+        <v>325242.43</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>14281.36</v>
+      </c>
+      <c r="F74" s="10" t="n">
+        <v>502291.14</v>
       </c>
     </row>
     <row r="75">
@@ -3233,17 +3086,14 @@
           <t>Materialaufwand</t>
         </is>
       </c>
-      <c r="D75" s="10">
-        <f>-1*INDEX('[GuV.xlsx]GuV'!$F$11:$Q$11,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E75" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",-1*INDEX('[GuV.xlsx]GuV'!$F$11:$Q$11,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F75" s="10">
-        <f>-1*'[GuV.xlsx]GuV'!D11</f>
-        <v/>
+      <c r="D75" s="10" t="n">
+        <v>1735737.84</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>1436882.3</v>
+      </c>
+      <c r="F75" s="10" t="n">
+        <v>13430817.92</v>
       </c>
     </row>
     <row r="76">
@@ -3252,17 +3102,14 @@
           <t>Personalaufwand</t>
         </is>
       </c>
-      <c r="D76" s="10">
-        <f>-1*INDEX('[GuV.xlsx]GuV'!$F$12:$Q$12,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E76" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",-1*INDEX('[GuV.xlsx]GuV'!$F$12:$Q$12,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F76" s="10">
-        <f>-1*'[GuV.xlsx]GuV'!D12</f>
-        <v/>
+      <c r="D76" s="10" t="n">
+        <v>356776.51</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>399129.54</v>
+      </c>
+      <c r="F76" s="10" t="n">
+        <v>3427005.18</v>
       </c>
     </row>
     <row r="77">
@@ -3271,17 +3118,14 @@
           <t>Sonstiger Aufwand</t>
         </is>
       </c>
-      <c r="D77" s="10">
-        <f>-1*INDEX('[GuV.xlsx]GuV'!$F$13:$Q$13,1,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E77" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",-1*INDEX('[GuV.xlsx]GuV'!$F$13:$Q$13,1,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-      <c r="F77" s="10">
-        <f>-1*'[GuV.xlsx]GuV'!D13</f>
-        <v/>
+      <c r="D77" s="10" t="n">
+        <v>258426.01</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>191884.67</v>
+      </c>
+      <c r="F77" s="10" t="n">
+        <v>2188667.93</v>
       </c>
     </row>
     <row r="78">
@@ -3290,17 +3134,14 @@
           <t>Gesamtaufwand</t>
         </is>
       </c>
-      <c r="D78" s="10">
-        <f>SUM(D75:D77)-D70</f>
-        <v/>
-      </c>
-      <c r="E78" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",SUM(E75:E77)-E70)</f>
-        <v/>
-      </c>
-      <c r="F78" s="10">
-        <f>SUM(F75:F77)-F70</f>
-        <v/>
+      <c r="D78" s="10" t="n">
+        <v>2360042.36</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>2037006.36</v>
+      </c>
+      <c r="F78" s="10" t="n">
+        <v>19131269.8</v>
       </c>
     </row>
     <row r="79">
@@ -3309,17 +3150,18 @@
           <t>Produktive Stunden</t>
         </is>
       </c>
-      <c r="D79" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$D$7:$D$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E79" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$D$7:$D$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F79" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$D$7:INDEX('[Stunden.xlsx]Stunden'!$D$7:$D$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$D$7:INDEX('[Stunden.xlsx]Stunden'!$D$7:$D$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D79" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F79" s="10" t="n">
+        <v>24365.75</v>
       </c>
     </row>
     <row r="80">
@@ -3328,17 +3170,18 @@
           <t>Gesamtstunden</t>
         </is>
       </c>
-      <c r="D80" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$I$7:$I$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E80" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$I$7:$I$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F80" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$I$7:INDEX('[Stunden.xlsx]Stunden'!$I$7:$I$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$I$7:INDEX('[Stunden.xlsx]Stunden'!$I$7:$I$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D80" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E80" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F80" s="10" t="n">
+        <v>34691.75</v>
       </c>
     </row>
     <row r="81">
@@ -3347,17 +3190,18 @@
           <t>Krankheit</t>
         </is>
       </c>
-      <c r="D81" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$G$7:$G$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E81" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$G$7:$G$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F81" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$G$7:INDEX('[Stunden.xlsx]Stunden'!$G$7:$G$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$G$7:INDEX('[Stunden.xlsx]Stunden'!$G$7:$G$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E81" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F81" s="10" t="n">
+        <v>2564</v>
       </c>
     </row>
     <row r="82">
@@ -3366,17 +3210,18 @@
           <t>Urlaub</t>
         </is>
       </c>
-      <c r="D82" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$F$7:$F$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E82" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$F$7:$F$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F82" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$F$7:INDEX('[Stunden.xlsx]Stunden'!$F$7:$F$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$F$7:INDEX('[Stunden.xlsx]Stunden'!$F$7:$F$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D82" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F82" s="10" t="n">
+        <v>3059</v>
       </c>
     </row>
     <row r="83">
@@ -3385,17 +3230,18 @@
           <t>Feiertag</t>
         </is>
       </c>
-      <c r="D83" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$H$7:$H$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E83" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$H$7:$H$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F83" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$H$7:INDEX('[Stunden.xlsx]Stunden'!$H$7:$H$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$H$7:INDEX('[Stunden.xlsx]Stunden'!$H$7:$H$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D83" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F83" s="10" t="n">
+        <v>1967</v>
       </c>
     </row>
     <row r="84">
@@ -3404,17 +3250,18 @@
           <t>Unproduktiv</t>
         </is>
       </c>
-      <c r="D84" s="10">
-        <f>IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$E$7:$E$18,'[Steuerung.xlsx]Steuerung'!$F$7,1),"n.a.")</f>
-        <v/>
-      </c>
-      <c r="E84" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(OR(COUNTIFS('[Import Stunden.xlsx]Import Stunden'!$C$7:$C$8,'[Steuerung.xlsx]Steuerung'!$F$6,'[Import Stunden.xlsx]Import Stunden'!$D$7:$D$8,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0,COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)&gt;0),INDEX('[Stunden.xlsx]Stunden'!$E$7:$E$18,'[Steuerung.xlsx]Steuerung'!$F$7-1,1),"n.a."))</f>
-        <v/>
-      </c>
-      <c r="F84" s="10">
-        <f>IF(COUNT('[Stunden.xlsx]Stunden'!$E$7:INDEX('[Stunden.xlsx]Stunden'!$E$7:$E$18,'[Steuerung.xlsx]Steuerung'!$F$7,1))=0,"n.a.",SUM('[Stunden.xlsx]Stunden'!$E$7:INDEX('[Stunden.xlsx]Stunden'!$E$7:$E$18,'[Steuerung.xlsx]Steuerung'!$F$7,1)))</f>
-        <v/>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F84" s="10" t="n">
+        <v>1658</v>
       </c>
     </row>
     <row r="85">
@@ -3423,17 +3270,18 @@
           <t>Mitarbeiter</t>
         </is>
       </c>
-      <c r="D85" s="10">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7)=0,"n.a.",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7))</f>
-        <v/>
-      </c>
-      <c r="E85" s="10">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)=0,"n.a.",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,'[Steuerung.xlsx]Steuerung'!$F$7-1)))</f>
-        <v/>
-      </c>
-      <c r="F85" s="10">
-        <f>IF(COUNTIFS('[D KLR.xlsx]D KLR'!$A$1142:$A$1146,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7)=0,"n.a.",SUMIFS('[D KLR.xlsx]D KLR'!$M$1142:$M$1146,'[D KLR.xlsx]D KLR'!$A$1142:$A$1146,"&lt;="&amp;'[Steuerung.xlsx]Steuerung'!$F$7))</f>
-        <v/>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
+        <is>
+          <t>n.a.</t>
+        </is>
+      </c>
+      <c r="F85" s="10" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="86">
@@ -3442,15 +3290,15 @@
           <t>Vorräte netto</t>
         </is>
       </c>
-      <c r="D86">
-        <f>SUMIFS('[D Liquidität.xlsx]D Liquidität'!$F$632:$F$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,'[Steuerung.xlsx]Steuerung'!$F$7)</f>
-        <v/>
-      </c>
-      <c r="E86">
-        <f>IF('[Steuerung.xlsx]Steuerung'!$F$7=1,"n.a.",SUMIFS('[D Liquidität.xlsx]D Liquidität'!$F$632:$F$655,'[D Liquidität.xlsx]D Liquidität'!$A$632:$A$655,'[Steuerung.xlsx]Steuerung'!$F$6,'[D Liquidität.xlsx]D Liquidität'!$B$632:$B$655,'[Steuerung.xlsx]Steuerung'!$F$7-1))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="D86" t="n">
+        <v>-1404058.17</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-1165833.71</v>
+      </c>
+    </row>
+    <row r="87"/>
+    <row r="88"/>
     <row r="89">
       <c r="C89" t="inlineStr">
         <is>
